--- a/语音/有水调试.xlsx
+++ b/语音/有水调试.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="125">
   <si>
     <t>操作名称</t>
   </si>
@@ -44,7 +44,7 @@
     <t>空载摆动试验</t>
   </si>
   <si>
-    <t>检查蜗壳压力与尾水管压力，蜗壳0.12兆帕，支持盖0.9兆帕，尾水管压力0.05兆帕，验证机组已充水，具备启动条件</t>
+    <t>检查蜗壳压力与尾水管压力，蜗壳0.12兆帕，支持盖0.09兆帕，尾水管压力0.05兆帕，验证机组已充水，具备启动条件</t>
   </si>
   <si>
     <t>检查蜗壳压力与尾水管压力，验证机组已充水，具备启动条件</t>
@@ -66,7 +66,7 @@
         <rFont val="Microsoft YaHei"/>
         <charset val="134"/>
       </rPr>
-      <t>0.12兆帕，支持盖0.9兆帕，尾水管压力0.05兆帕</t>
+      <t>0.12兆帕，支持盖0.09兆帕，尾水管压力0.05兆帕</t>
     </r>
   </si>
   <si>
@@ -118,10 +118,13 @@
     <t>已完成水头设置</t>
   </si>
   <si>
-    <t>使用预设值在参数设置界面设置频率调节PID参数</t>
-  </si>
-  <si>
-    <t>已完成频率调节PID参数设置</t>
+    <t>使用预设值在参数设置界面设置频率调节P.I.D参数</t>
+  </si>
+  <si>
+    <t>设置路径"参数设定", "P.I.D参数整定", "频率调节P.I.D参数设定"</t>
+  </si>
+  <si>
+    <t>已完成频率调节P.I.D参数设置</t>
   </si>
   <si>
     <t>操作导叶工作模式旋钮指向“电手动”位置</t>
@@ -154,121 +157,133 @@
     <t>导叶工作模式旋钮已指向“自动”位置</t>
   </si>
   <si>
-    <t>进入空载扰动实验界面，点击开始实验，进行A套空载扰动实验</t>
+    <t>进入空载频率摆动试验界面，进行A机空载频率摆动试验</t>
   </si>
   <si>
     <t>点击"试验", "空载频率摆动试验","电气开限", "跟踪频给","试验开始"</t>
   </si>
   <si>
-    <t>本次试验，最高频率50.05赫兹，最低频率 49.88赫兹</t>
-  </si>
-  <si>
-    <t>转速摆动率不超过0.3%</t>
-  </si>
-  <si>
-    <t>已完成A机摆动实验，实验合格</t>
+    <t>最高频率50.05赫兹，最低频率 49.88赫兹,转速摆动率0.24%</t>
+  </si>
+  <si>
+    <t>已完成A机摆动试验，试验合格</t>
   </si>
   <si>
     <t>查看A机频率摆动试验报告</t>
   </si>
   <si>
-    <t>已查看A机频率摆动试验结果报告</t>
+    <t>已查看A机频率摆动试验报告</t>
+  </si>
+  <si>
+    <t>控制器选择切至B机主用</t>
+  </si>
+  <si>
+    <t>控制器选择已切换到B机</t>
+  </si>
+  <si>
+    <t>进入空载频率摆动试验界面，进行B机空载频率摆动试验</t>
+  </si>
+  <si>
+    <t>点击 "试验开始"</t>
+  </si>
+  <si>
+    <t>已完成B机摆动试验，试验合格</t>
+  </si>
+  <si>
+    <t>查看B机频率摆动试验报告</t>
+  </si>
+  <si>
+    <t>已查看B机频率摆动试验报告</t>
+  </si>
+  <si>
+    <t>从B机主用切至A机主用</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>已完成空载频率摆动试验，接下来进行自动开停机试验，空载频率扰动试验</t>
+  </si>
+  <si>
+    <t>已切至A机主用</t>
+  </si>
+  <si>
+    <t>自动开停机试验，空载频率扰动试验</t>
+  </si>
+  <si>
+    <t>操作控制权限旋钮指向“远方”位置</t>
+  </si>
+  <si>
+    <t>控制权限切换旋钮已切换到远方</t>
+  </si>
+  <si>
+    <t>打开LCUA1柜柜门</t>
+  </si>
+  <si>
+    <t>已打开LCUA1柜柜门</t>
+  </si>
+  <si>
+    <t>在LCUA1柜控制界面，发出停机令</t>
+  </si>
+  <si>
+    <t>已发送停机令</t>
+  </si>
+  <si>
+    <t>查看A机停机事件分析报告</t>
+  </si>
+  <si>
+    <t>已查看A机停机事件分析报告</t>
+  </si>
+  <si>
+    <t>在LCUA1柜控制界面，发出开机令</t>
+  </si>
+  <si>
+    <t>已发送开机令</t>
+  </si>
+  <si>
+    <t>查看A机开机性能报告</t>
+  </si>
+  <si>
+    <t>已查看A机开机性能报告</t>
+  </si>
+  <si>
+    <t>使用预设值在参数设置界面设置空载P.I.D参数</t>
+  </si>
+  <si>
+    <t>已完成空载P.I.D参数设置</t>
+  </si>
+  <si>
+    <t>进入空载扰动试验界面，进行A套空载频率扰动试验</t>
+  </si>
+  <si>
+    <t>点击"试验", "空载频率扰动试验", "频率给定增加", "跟踪频给","试验开始"</t>
+  </si>
+  <si>
+    <t>最低频率49.91，最高频率52.19，超调量：9.36%，调节时间：13.99秒</t>
+  </si>
+  <si>
+    <t>已完成A套空载频率扰动试验，试验合格</t>
+  </si>
+  <si>
+    <t>查看A套空载频率扰动试验报告</t>
+  </si>
+  <si>
+    <t>已查看A套空载频率扰动试验报告</t>
   </si>
   <si>
     <t>从A机主用切至B机主用</t>
   </si>
   <si>
-    <t>控制器选择已切换到B机</t>
-  </si>
-  <si>
-    <t>进入空载扰动实验界面，点击开始实验，进行B套空载扰动实验</t>
-  </si>
-  <si>
-    <t>点击 "试验开始"</t>
-  </si>
-  <si>
-    <t>本次试验，最高频率50.05f赫兹，最低频率 49.88f赫兹</t>
-  </si>
-  <si>
-    <t>已完成B摆动实验，实验合格</t>
-  </si>
-  <si>
-    <t>查看B机频率摆动试验报告</t>
-  </si>
-  <si>
-    <t>已查看B机频率摆动试验报告</t>
-  </si>
-  <si>
-    <t>从B机主用切至A机主用</t>
-  </si>
-  <si>
-    <t>已完成空载频率摆动试验，接下来进行自动开停机试验，空载频率扰动试验</t>
-  </si>
-  <si>
-    <t>自动开停机试验，空载频率扰动试验</t>
-  </si>
-  <si>
-    <t>操作控制权限旋钮指向“远方”位置</t>
-  </si>
-  <si>
-    <t>控制权限切换旋钮已切换到远方</t>
-  </si>
-  <si>
-    <t>打开LCUA1柜柜门</t>
-  </si>
-  <si>
-    <t>已打开LCUA1柜柜门</t>
-  </si>
-  <si>
-    <t>在LCUA1柜控制界面，发出停机令</t>
-  </si>
-  <si>
-    <t>已发送停机令</t>
-  </si>
-  <si>
-    <t>查看A机停机事件分析报告</t>
-  </si>
-  <si>
-    <t>已查看A机停机事件分析报告</t>
-  </si>
-  <si>
-    <t>在LCUA1柜控制界面，发出开机令</t>
-  </si>
-  <si>
-    <t>已发送开机令</t>
-  </si>
-  <si>
-    <t>查看A机开机性能报告</t>
-  </si>
-  <si>
-    <t>已查看A机开机性能报告</t>
-  </si>
-  <si>
-    <t>使用预设值在参数设置界面设置空载PID参数</t>
-  </si>
-  <si>
-    <t>已完成空载PID参数设置</t>
-  </si>
-  <si>
-    <t>进入空载扰动实验界面，进行A套空载频率扰动试验</t>
-  </si>
-  <si>
-    <t>点击"试验", "空载频率摆动试验", "电气开限", "跟踪频给","试验开始"</t>
-  </si>
-  <si>
-    <t>本次试验，最高频率50.05赫兹，最低频率49.88赫兹,频率偏差0.24%</t>
-  </si>
-  <si>
-    <t>已完成自动摆动实验，实验合格</t>
-  </si>
-  <si>
-    <t>查看A套空载频率扰动试验报告</t>
-  </si>
-  <si>
-    <t>已查看A套空载频率扰动试验报告</t>
-  </si>
-  <si>
-    <t>进入空载扰动实验界面，进行B套空载频率扰动试验</t>
+    <t>进入空载扰动试验界面，进行B套空载频率扰动试验</t>
+  </si>
+  <si>
+    <t>点击 "频率给定减少", "跟踪频给","试验开始"</t>
+  </si>
+  <si>
+    <t>最低频率49.92，最高频率51.95，超调量：0.08%，调节时间：9.56秒</t>
+  </si>
+  <si>
+    <t>已完成B套空载频率扰动试验，试验合格</t>
   </si>
   <si>
     <t>查看B套空载频率扰动试验报告</t>
@@ -283,6 +298,9 @@
     <t>已完成自动开停机试验，空载频率扰动试验。在进行甩负荷试验前，假设机组已并网带负荷，稳定运行30分钟无异常</t>
   </si>
   <si>
+    <t>已发出断路器合令</t>
+  </si>
+  <si>
     <t>甩负荷试验</t>
   </si>
   <si>
@@ -298,6 +316,12 @@
     <t>已完成油压装置自动控制屏检查</t>
   </si>
   <si>
+    <t>打开1号发电机测温制动屏柜门</t>
+  </si>
+  <si>
+    <t>已打开1号发电机测温制动屏</t>
+  </si>
+  <si>
     <t>检查1号发电机测温制动屏指示灯，交流直流电源指示灯亮，复位投入灯亮，制动投入熄灭，转子落下灯亮，转子投入熄灭</t>
   </si>
   <si>
@@ -322,7 +346,13 @@
     <t>已完成1号发电机测温制动屏气压表计检查</t>
   </si>
   <si>
-    <t>在甩负荷实验界面，按额定负荷的25%进行试验</t>
+    <t>关闭1号发电机测温制动屏柜门</t>
+  </si>
+  <si>
+    <t>已关闭1号发电机测温制动屏</t>
+  </si>
+  <si>
+    <t>在甩负荷试验界面，按额定负荷的25%进行试验</t>
   </si>
   <si>
     <t>点击"试验", "甩负荷试验", "试验开始"</t>
@@ -331,7 +361,7 @@
     <t>最高频率：55.40赫兹,最低频率：49.20赫兹,不动时间：0.05秒，调整时间：18.60秒</t>
   </si>
   <si>
-    <t>已完成甩负荷实验，实验合格</t>
+    <t>已完成甩负荷试验，试验合格</t>
   </si>
   <si>
     <t>查看甩25%负荷性能曲线报告</t>
@@ -340,7 +370,7 @@
     <t>已查看甩25%负荷性能曲线报告</t>
   </si>
   <si>
-    <t>在甩负荷实验界面，按额定负荷的50%进行试验</t>
+    <t>在甩负荷试验界面，按额定负荷的50%进行试验</t>
   </si>
   <si>
     <t>最高频率：59.85赫兹,最低频率：48.60赫兹,不动时间：0.06秒，调整时间：32.40秒</t>
@@ -352,7 +382,7 @@
     <t>已查看甩50%负荷性能曲线报告</t>
   </si>
   <si>
-    <t>在甩负荷实验界面，按额定负荷的75%进行试验</t>
+    <t>在甩负荷试验界面，按额定负荷的75%进行试验</t>
   </si>
   <si>
     <t>最高频率：61.10赫兹,最低频率：47.30赫兹,不动时间：0.07秒，调整时间：44.80秒</t>
@@ -364,7 +394,7 @@
     <t>已查看甩75%负荷性能曲线报告</t>
   </si>
   <si>
-    <t>在甩负荷实验界面，按额定负荷的100%进行试验</t>
+    <t>在甩负荷试验界面，按额定负荷的100%进行试验</t>
   </si>
   <si>
     <t>最高频率：62.68赫兹,最低频率：46.23赫兹,不动时间：0.07秒，调整时间：54.36秒</t>
@@ -383,6 +413,9 @@
   </si>
   <si>
     <t>关闭LCUA1柜柜门</t>
+  </si>
+  <si>
+    <t>已关闭LCUA1柜柜门</t>
   </si>
   <si>
     <t>已完成1号水轮机调速器有水调试，所有试验曲线及结论可在图纸中复查</t>
@@ -398,7 +431,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -430,6 +463,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFA31515"/>
+      <name val="新宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -893,152 +932,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1057,6 +1096,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1442,7 +1485,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I112"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11.0083333333333" style="1" customWidth="1"/>
@@ -1679,105 +1722,103 @@
       </c>
     </row>
     <row r="17" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A17" s="2">
-        <v>17</v>
-      </c>
+      <c r="A17" s="2"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" ht="30.5" customHeight="1" spans="1:5">
       <c r="A18" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4"/>
-      <c r="C18" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="C18" s="5"/>
       <c r="D18" s="5" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" ht="30.5" customHeight="1" spans="1:5">
       <c r="A19" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
+      <c r="C19" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="D19" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" ht="30.5" customHeight="1" spans="1:5">
       <c r="A20" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="C20" s="5"/>
       <c r="D20" s="5" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" ht="30.5" customHeight="1" spans="1:5">
       <c r="A21" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="D21" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" ht="47" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="30.5" customHeight="1" spans="1:5">
       <c r="A22" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="5" t="s">
-        <v>31</v>
-      </c>
       <c r="E22" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" ht="47" customHeight="1" spans="1:5">
       <c r="A23" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
+      <c r="C23" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D23" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="47" customHeight="1" spans="1:5">
       <c r="A24" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
@@ -1785,68 +1826,68 @@
         <v>33</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" ht="30.5" customHeight="1" spans="1:5">
       <c r="A25" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4"/>
-      <c r="C25" s="5" t="s">
-        <v>34</v>
-      </c>
+      <c r="C25" s="5"/>
       <c r="D25" s="5" t="s">
         <v>34</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" ht="30.5" customHeight="1" spans="1:5">
       <c r="A26" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
+      <c r="C26" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="D26" s="5" t="s">
         <v>35</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" ht="47" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="30.5" customHeight="1" spans="1:5">
       <c r="A27" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4"/>
-      <c r="C27" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="C27" s="5"/>
       <c r="D27" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" ht="30.5" customHeight="1" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" ht="47" customHeight="1" spans="1:5">
       <c r="A28" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
+      <c r="C28" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="D28" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" ht="30.5" customHeight="1" spans="1:5">
       <c r="A29" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
@@ -1859,7 +1900,7 @@
     </row>
     <row r="30" ht="30.5" customHeight="1" spans="1:5">
       <c r="A30" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
@@ -1974,7 +2015,7 @@
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>8</v>
@@ -1982,315 +2023,311 @@
     </row>
     <row r="39" ht="30.5" customHeight="1" spans="1:5">
       <c r="A39" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" ht="30.5" customHeight="1" spans="1:5">
       <c r="A40" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" s="4"/>
-      <c r="C40" s="5"/>
+      <c r="C40" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="D40" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" ht="30.5" customHeight="1" spans="1:5">
       <c r="A41" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" s="4"/>
-      <c r="C41" s="5" t="s">
-        <v>49</v>
-      </c>
+      <c r="C41" s="5"/>
       <c r="D41" s="5" t="s">
         <v>49</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" ht="30.5" customHeight="1" spans="1:5">
       <c r="A42" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="4"/>
-      <c r="C42" s="5"/>
+      <c r="C42" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="D42" s="5" t="s">
         <v>50</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A43" s="2">
-        <v>43</v>
-      </c>
+      <c r="A43" s="2"/>
       <c r="B43" s="4"/>
-      <c r="C43" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="C43" s="5"/>
       <c r="D43" s="5" t="s">
         <v>51</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A44" s="2">
-        <v>44</v>
-      </c>
+      <c r="A44" s="2"/>
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
         <v>52</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" ht="30.5" customHeight="1" spans="1:5">
       <c r="A45" s="2">
-        <v>45</v>
-      </c>
-      <c r="B45" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>54</v>
-      </c>
       <c r="E45" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" ht="30.5" customHeight="1" spans="1:5">
       <c r="A46" s="2">
-        <v>46</v>
-      </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="5"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="D46" s="5" t="s">
         <v>55</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" ht="30.5" customHeight="1" spans="1:5">
       <c r="A47" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47" s="4"/>
-      <c r="C47" s="5" t="s">
-        <v>56</v>
-      </c>
+      <c r="C47" s="5"/>
       <c r="D47" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" ht="30.5" customHeight="1" spans="1:5">
       <c r="A48" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48" s="4"/>
-      <c r="C48" s="5"/>
+      <c r="C48" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="D48" s="5" t="s">
         <v>57</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" ht="30.5" customHeight="1" spans="1:5">
       <c r="A49" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49" s="4"/>
-      <c r="C49" s="5" t="s">
-        <v>58</v>
-      </c>
+      <c r="C49" s="5"/>
       <c r="D49" s="5" t="s">
         <v>58</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" ht="30.5" customHeight="1" spans="1:5">
       <c r="A50" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50" s="4"/>
-      <c r="C50" s="5"/>
+      <c r="C50" s="5" t="s">
+        <v>59</v>
+      </c>
       <c r="D50" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" ht="30.5" customHeight="1" spans="1:5">
       <c r="A51" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51" s="4"/>
-      <c r="C51" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="C51" s="5"/>
       <c r="D51" s="5" t="s">
         <v>60</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" ht="47" customHeight="1" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" ht="30.5" customHeight="1" spans="1:5">
       <c r="A52" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" s="4"/>
-      <c r="C52" s="5"/>
+      <c r="C52" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="D52" s="5" t="s">
         <v>61</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" ht="47" customHeight="1" spans="1:5">
       <c r="A53" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53" s="4"/>
-      <c r="C53" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="C53" s="5"/>
       <c r="D53" s="5" t="s">
         <v>62</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" ht="30.5" customHeight="1" spans="1:5">
       <c r="A54" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54" s="4"/>
-      <c r="C54" s="5"/>
+      <c r="C54" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="D54" s="5" t="s">
         <v>63</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" ht="30.5" customHeight="1" spans="1:5">
       <c r="A55" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="4"/>
-      <c r="C55" s="5" t="s">
-        <v>64</v>
-      </c>
+      <c r="C55" s="5"/>
       <c r="D55" s="5" t="s">
         <v>64</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" ht="47" customHeight="1" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" ht="30.5" customHeight="1" spans="1:5">
       <c r="A56" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" s="4"/>
-      <c r="C56" s="5"/>
+      <c r="C56" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="D56" s="5" t="s">
         <v>65</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" ht="47" customHeight="1" spans="1:5">
       <c r="A57" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="4"/>
-      <c r="C57" s="5" t="s">
-        <v>66</v>
-      </c>
+      <c r="C57" s="5"/>
       <c r="D57" s="5" t="s">
         <v>66</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" ht="30.5" customHeight="1" spans="1:5">
       <c r="A58" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="4"/>
-      <c r="C58" s="5"/>
+      <c r="C58" s="5" t="s">
+        <v>67</v>
+      </c>
       <c r="D58" s="5" t="s">
         <v>67</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" ht="80" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" ht="30.5" customHeight="1" spans="1:5">
       <c r="A59" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59" s="4"/>
-      <c r="C59" s="5" t="s">
-        <v>68</v>
-      </c>
+      <c r="C59" s="5"/>
       <c r="D59" s="5" t="s">
         <v>68</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" ht="47" customHeight="1" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" ht="80" customHeight="1" spans="1:5">
       <c r="A60" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60" s="4"/>
-      <c r="C60" s="5"/>
+      <c r="C60" s="5" t="s">
+        <v>69</v>
+      </c>
       <c r="D60" s="5" t="s">
         <v>69</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" ht="47" customHeight="1" spans="1:5">
       <c r="A61" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="5"/>
@@ -2303,109 +2340,109 @@
     </row>
     <row r="62" ht="30.5" customHeight="1" spans="1:5">
       <c r="A62" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="5"/>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="8" t="s">
         <v>71</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" ht="30.5" customHeight="1" spans="1:5">
       <c r="A63" s="2">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63" s="4"/>
-      <c r="C63" s="5" t="s">
-        <v>72</v>
-      </c>
+      <c r="C63" s="5"/>
       <c r="D63" s="5" t="s">
         <v>72</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" ht="30.5" customHeight="1" spans="1:5">
       <c r="A64" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" s="4"/>
-      <c r="C64" s="5"/>
+      <c r="C64" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="D64" s="5" t="s">
         <v>73</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" ht="30.5" customHeight="1" spans="1:5">
       <c r="A65" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65" s="4"/>
-      <c r="C65" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="C65" s="5"/>
       <c r="D65" s="5" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" ht="30.5" customHeight="1" spans="1:5">
       <c r="A66" s="2">
+        <v>65</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5" t="s">
+      <c r="B67" s="4"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" ht="80" customHeight="1" spans="1:5">
-      <c r="A67" s="2">
+      <c r="E67" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" ht="80" customHeight="1" spans="1:5">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" ht="47" customHeight="1" spans="1:5">
-      <c r="A68" s="2">
+      <c r="B68" s="4"/>
+      <c r="C68" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" ht="47" customHeight="1" spans="1:5">
+      <c r="A69" s="2">
         <v>68</v>
-      </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E68" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A69" s="2">
-        <v>69</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="5"/>
       <c r="D69" s="5" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>8</v>
@@ -2413,592 +2450,715 @@
     </row>
     <row r="70" ht="30.5" customHeight="1" spans="1:5">
       <c r="A70" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="5"/>
-      <c r="D70" s="5" t="s">
-        <v>71</v>
+      <c r="D70" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" ht="30.5" customHeight="1" spans="1:5">
       <c r="A71" s="2">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" s="4"/>
-      <c r="C71" s="5" t="s">
-        <v>75</v>
-      </c>
+      <c r="C71" s="5"/>
       <c r="D71" s="5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" ht="30.5" customHeight="1" spans="1:5">
       <c r="A72" s="2">
+        <v>71</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A73" s="2">
         <v>72</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" ht="63.5" customHeight="1" spans="1:5">
-      <c r="A73" s="2">
+      <c r="B73" s="4"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" ht="63.5" customHeight="1" spans="1:5">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" ht="47" customHeight="1" spans="1:5">
-      <c r="A74" s="2">
-        <v>74</v>
-      </c>
       <c r="B74" s="4"/>
-      <c r="C74" s="5"/>
+      <c r="C74" s="5" t="s">
+        <v>82</v>
+      </c>
       <c r="D74" s="5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="75" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A75" s="2">
-        <v>75</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>80</v>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" ht="63.5" customHeight="1" spans="1:5">
+      <c r="A75" s="2"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="5" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A76" s="2">
-        <v>76</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" ht="63.5" customHeight="1" spans="1:5">
+      <c r="A76" s="2"/>
       <c r="B76" s="4"/>
       <c r="C76" s="5"/>
       <c r="D76" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" ht="30.5" customHeight="1" spans="1:5">
+    <row r="77" ht="47" customHeight="1" spans="1:5">
       <c r="A77" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B77" s="4"/>
       <c r="C77" s="5"/>
       <c r="D77" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="78" ht="63.5" customHeight="1" spans="1:5">
+    <row r="78" ht="30.5" customHeight="1" spans="1:5">
       <c r="A78" s="2">
-        <v>78</v>
-      </c>
-      <c r="B78" s="4"/>
+        <v>75</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>85</v>
+      </c>
       <c r="C78" s="5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="79" ht="47" customHeight="1" spans="1:5">
+    <row r="79" ht="30.5" customHeight="1" spans="1:5">
       <c r="A79" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B79" s="4"/>
       <c r="C79" s="5"/>
       <c r="D79" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="80" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A80" s="2">
-        <v>80</v>
-      </c>
+      <c r="A80" s="2"/>
       <c r="B80" s="4"/>
       <c r="C80" s="5"/>
       <c r="D80" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="81" ht="63.5" customHeight="1" spans="1:5">
-      <c r="A81" s="2">
-        <v>81</v>
-      </c>
+    <row r="81" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A81" s="2"/>
       <c r="B81" s="4"/>
-      <c r="C81" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>89</v>
+      <c r="C81" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="82" ht="47" customHeight="1" spans="1:5">
+    <row r="82" ht="30.5" customHeight="1" spans="1:5">
       <c r="A82" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B82" s="4"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5" t="s">
-        <v>90</v>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9" t="s">
+        <v>91</v>
       </c>
       <c r="E82" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" ht="63.5" customHeight="1" spans="1:5">
+      <c r="A83" s="2">
+        <v>78</v>
+      </c>
+      <c r="B83" s="4"/>
+      <c r="C83" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" ht="47" customHeight="1" spans="1:5">
+      <c r="A84" s="2">
+        <v>79</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="E84" s="4" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="83" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A83" s="2">
-        <v>83</v>
-      </c>
-      <c r="B83" s="4"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A84" s="2">
-        <v>84</v>
-      </c>
-      <c r="B84" s="4"/>
-      <c r="C84" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D84" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E84" s="4" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="85" ht="30.5" customHeight="1" spans="1:5">
       <c r="A85" s="2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B85" s="4"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5" t="s">
-        <v>93</v>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="E85" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" ht="63.5" customHeight="1" spans="1:5">
+      <c r="A86" s="2">
+        <v>81</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" ht="47" customHeight="1" spans="1:5">
+      <c r="A87" s="2">
+        <v>82</v>
+      </c>
+      <c r="B87" s="4"/>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="E87" s="4" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="86" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A86" s="2">
-        <v>86</v>
-      </c>
-      <c r="B86" s="4"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="87" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A87" s="2">
-        <v>87</v>
-      </c>
-      <c r="B87" s="4"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="88" ht="30.5" customHeight="1" spans="1:5">
       <c r="A88" s="2">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B88" s="4"/>
-      <c r="C88" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="D88" s="5" t="s">
-        <v>96</v>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A89" s="2">
-        <v>89</v>
-      </c>
+      <c r="A89" s="2"/>
       <c r="B89" s="4"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5" t="s">
-        <v>97</v>
+      <c r="C89" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" ht="47" customHeight="1" spans="1:5">
-      <c r="A90" s="2">
-        <v>90</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>98</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A90" s="2"/>
+      <c r="B90" s="4"/>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9" t="s">
+        <v>101</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" ht="30.5" customHeight="1" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1" spans="1:5">
       <c r="A91" s="2">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="B91" s="4"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5" t="s">
-        <v>46</v>
+      <c r="C91" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="92" ht="30.5" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" ht="30" customHeight="1" spans="1:5">
       <c r="A92" s="2">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="5"/>
       <c r="D92" s="5" t="s">
-        <v>99</v>
+        <v>52</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="93" ht="47" customHeight="1" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" ht="30.5" customHeight="1" spans="1:5">
       <c r="A93" s="2">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="B93" s="4"/>
-      <c r="C93" s="5"/>
+      <c r="C93" s="5" t="s">
+        <v>102</v>
+      </c>
       <c r="D93" s="5" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" ht="30.5" customHeight="1" spans="1:5">
       <c r="A94" s="2">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B94" s="4"/>
-      <c r="C94" s="5" t="s">
-        <v>100</v>
-      </c>
+      <c r="C94" s="5"/>
       <c r="D94" s="5" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" ht="30.5" customHeight="1" spans="1:5">
       <c r="A95" s="2">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="5"/>
       <c r="D95" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" ht="30.5" customHeight="1" spans="1:5">
       <c r="A96" s="2">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B96" s="4"/>
-      <c r="C96" s="5" t="s">
-        <v>102</v>
-      </c>
+      <c r="C96" s="5"/>
       <c r="D96" s="5" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" ht="30.5" customHeight="1" spans="1:5">
       <c r="A97" s="2">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B97" s="4"/>
-      <c r="C97" s="5"/>
+      <c r="C97" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="D97" s="5" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" ht="30.5" customHeight="1" spans="1:5">
       <c r="A98" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="5"/>
       <c r="D98" s="5" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="99" ht="30.5" customHeight="1" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" ht="47" customHeight="1" spans="1:5">
       <c r="A99" s="2">
-        <v>99</v>
-      </c>
-      <c r="B99" s="4"/>
-      <c r="C99" s="5"/>
+        <v>92</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>108</v>
+      </c>
       <c r="D99" s="5" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" ht="30.5" customHeight="1" spans="1:5">
       <c r="A100" s="2">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B100" s="4"/>
-      <c r="C100" s="5" t="s">
-        <v>104</v>
-      </c>
+      <c r="C100" s="5"/>
       <c r="D100" s="5" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" ht="30.5" customHeight="1" spans="1:5">
       <c r="A101" s="2">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B101" s="4"/>
       <c r="C101" s="5"/>
       <c r="D101" s="5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" ht="47" customHeight="1" spans="1:5">
       <c r="A102" s="2">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B102" s="4"/>
-      <c r="C102" s="5" t="s">
-        <v>106</v>
-      </c>
+      <c r="C102" s="5"/>
       <c r="D102" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" ht="47" customHeight="1" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" ht="30.5" customHeight="1" spans="1:5">
       <c r="A103" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B103" s="4"/>
-      <c r="C103" s="5"/>
+      <c r="C103" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="D103" s="5" t="s">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" ht="30.5" customHeight="1" spans="1:5">
       <c r="A104" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="5"/>
       <c r="D104" s="5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" ht="30.5" customHeight="1" spans="1:5">
       <c r="A105" s="2">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B105" s="4"/>
-      <c r="C105" s="5"/>
+      <c r="C105" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="D105" s="5" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" ht="47" customHeight="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" ht="30.5" customHeight="1" spans="1:5">
       <c r="A106" s="2">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B106" s="4"/>
-      <c r="C106" s="5" t="s">
-        <v>108</v>
-      </c>
+      <c r="C106" s="5"/>
       <c r="D106" s="5" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" ht="30.5" customHeight="1" spans="1:5">
       <c r="A107" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B107" s="4"/>
       <c r="C107" s="5"/>
       <c r="D107" s="5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" ht="30.5" customHeight="1" spans="1:5">
       <c r="A108" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B108" s="4"/>
-      <c r="C108" s="5" t="s">
-        <v>110</v>
-      </c>
+      <c r="C108" s="5"/>
       <c r="D108" s="5" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" ht="30.5" customHeight="1" spans="1:5">
       <c r="A109" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B109" s="4"/>
-      <c r="C109" s="5"/>
+      <c r="C109" s="5" t="s">
+        <v>114</v>
+      </c>
       <c r="D109" s="5" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" ht="30.5" customHeight="1" spans="1:5">
       <c r="A110" s="2">
+        <v>103</v>
+      </c>
+      <c r="B110" s="4"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" ht="47" customHeight="1" spans="1:5">
+      <c r="A111" s="2">
+        <v>104</v>
+      </c>
+      <c r="B111" s="4"/>
+      <c r="C111" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" ht="47" customHeight="1" spans="1:5">
+      <c r="A112" s="2">
+        <v>105</v>
+      </c>
+      <c r="B112" s="4"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A113" s="2">
+        <v>106</v>
+      </c>
+      <c r="B113" s="4"/>
+      <c r="C113" s="5"/>
+      <c r="D113" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A114" s="2">
+        <v>107</v>
+      </c>
+      <c r="B114" s="4"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="115" ht="47" customHeight="1" spans="1:5">
+      <c r="A115" s="2">
+        <v>108</v>
+      </c>
+      <c r="B115" s="4"/>
+      <c r="C115" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D115" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A116" s="2">
+        <v>109</v>
+      </c>
+      <c r="B116" s="4"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="117" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A117" s="2">
         <v>110</v>
       </c>
-      <c r="B110" s="4"/>
-      <c r="C110" s="5" t="s">
+      <c r="B117" s="4"/>
+      <c r="C117" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="D117" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A118" s="2">
+        <v>111</v>
+      </c>
+      <c r="B118" s="4"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="119" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A119" s="2">
         <v>112</v>
       </c>
-      <c r="D110" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" ht="30.5" customHeight="1" spans="1:5">
-      <c r="A111" s="2">
-        <v>111</v>
-      </c>
-      <c r="B111" s="4"/>
-      <c r="C111" s="5"/>
-      <c r="D111" s="5" t="s">
+      <c r="B119" s="4"/>
+      <c r="C119" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D119" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" ht="30.5" customHeight="1" spans="1:5">
+      <c r="A120" s="2">
         <v>113</v>
       </c>
-      <c r="E111" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="112" ht="16.5" spans="1:5">
-      <c r="B112" s="5"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
+      <c r="B120" s="4"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" ht="16.5" spans="1:5">
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
+      <c r="D121" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" ht="33" spans="1:5">
+      <c r="D122" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="D27:E27 B25:B27 B28:C28 E28 B32 E31 B31:C31 B37:C37 B67:B68 B66:E66 E65 B65 B62:E62 B60:C60 E59:E60 E55:E56 B55:B59 B53:E54 B52:C52 E51:E52 B51 B46:E50 C45:E45 B42:C42 B8:B10 B11:E12 B13:B17 B1:E1 D36:E36 B36 B35:E35 E111 B111:C111 B108:E110 B107:C107 E106:E107 B106 B105:E105 E104 B104:C104 E102 B102 B91:B95 B84:B89 B82:C83 B81 B79:C80 B78 E77:E83 B77:C77 E75 B74:C74 E73 B70:B73" numberStoredAsText="1"/>
+    <ignoredError sqref="B18 E28:E29 B26:B28 B29:C29 B32 E31 B31:C31 B37:C37 B68:B69 B67:E67 E66 B66 B63:C63 E63 B61:C61 E60:E61 E56:E57 B56:B60 B54:E55 B53:C53 E52:E53 B52 B47:E51 C46:E46 B41:C41 B8:B10 B11:E12 B13:B16 B1:E1 E36 B36 B35:E35 E120 B120:C120 B117:E119 B116:C116 E113:E116 B115 B113:C114 E111 B111 B100:B104 B93:B98 B87:C88 B86 B84:C85 B83 E83:E88 B82:C82 E78 B77:C77 E74 B71:B74" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>